--- a/Shablon/MSO-X3104A.xlsx
+++ b/Shablon/MSO-X3104A.xlsx
@@ -5,7 +5,7 @@
   <workbookPr showInkAnnotation="0" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ITL\MEASControl\Shablon\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\my_doc\ITL\MEASControl\Shablon\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="192">
   <si>
     <t>Fном, МГц</t>
   </si>
@@ -787,21 +787,6 @@
   </si>
   <si>
     <t>_pres</t>
-  </si>
-  <si>
-    <t>АО "Гос МКБ "Вымпел" им. И.И. Торопова"</t>
-  </si>
-  <si>
-    <t>СГМетр, лаборатория средств электрических и радиотехнических измерений</t>
-  </si>
-  <si>
-    <t>125424, г.Москва, Волоколамское шоссе, дом 90, стр. 23</t>
-  </si>
-  <si>
-    <t>Уникальный номер об аккредитации в реестре аккредитованных лиц № РОСС СОБ 3.00231.2014</t>
-  </si>
-  <si>
-    <t>Тел.+7 (495) 491-05-31, 22-68, e-mail: ogmetr@vympelmkb.ru</t>
   </si>
   <si>
     <t>1 Внешний осмотр (п. 7.1): соответствует</t>
@@ -1155,6 +1140,45 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1170,47 +1194,8 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1549,72 +1534,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="52" t="s">
-        <v>190</v>
-      </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
+      <c r="A1" s="54"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="52" t="s">
-        <v>191</v>
-      </c>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
+      <c r="A2" s="54"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="52" t="s">
-        <v>192</v>
-      </c>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
+      <c r="A3" s="54"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="52" t="s">
-        <v>193</v>
-      </c>
-      <c r="B4" s="52"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="52"/>
+      <c r="A4" s="54"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" s="52" t="s">
-        <v>194</v>
-      </c>
-      <c r="B5" s="52"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
+      <c r="A5" s="54"/>
+      <c r="B5" s="54"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
     </row>
@@ -1642,17 +1617,17 @@
       <c r="J7" s="23"/>
     </row>
     <row r="8" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="42" t="str">
+      <c r="A8" s="55" t="str">
         <f>"Протокол поверки № 10/"&amp;C74&amp;"/"&amp;C11</f>
         <v>Протокол поверки № 10/_date/_numb</v>
       </c>
-      <c r="B8" s="42"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
+      <c r="B8" s="55"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="55"/>
+      <c r="E8" s="55"/>
+      <c r="F8" s="55"/>
+      <c r="G8" s="55"/>
+      <c r="H8" s="55"/>
       <c r="I8" s="41"/>
       <c r="J8" s="41"/>
     </row>
@@ -1669,10 +1644,10 @@
       <c r="J9" s="3"/>
     </row>
     <row r="10" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="45" t="s">
+      <c r="A10" s="58" t="s">
         <v>162</v>
       </c>
-      <c r="B10" s="45"/>
+      <c r="B10" s="58"/>
       <c r="C10" s="33" t="s">
         <v>163</v>
       </c>
@@ -1687,10 +1662,10 @@
       <c r="J10" s="3"/>
     </row>
     <row r="11" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="45" t="s">
+      <c r="A11" s="58" t="s">
         <v>165</v>
       </c>
-      <c r="B11" s="45"/>
+      <c r="B11" s="58"/>
       <c r="C11" s="37" t="s">
         <v>166</v>
       </c>
@@ -1703,16 +1678,16 @@
       <c r="J11" s="3"/>
     </row>
     <row r="12" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="45" t="s">
+      <c r="A12" s="58" t="s">
         <v>167</v>
       </c>
-      <c r="B12" s="45"/>
-      <c r="C12" s="46"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="46"/>
+      <c r="B12" s="58"/>
+      <c r="C12" s="59"/>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
       <c r="I12" s="11"/>
       <c r="J12" s="3"/>
     </row>
@@ -1721,22 +1696,22 @@
         <v>168</v>
       </c>
       <c r="B13" s="39"/>
-      <c r="C13" s="47" t="s">
+      <c r="C13" s="45" t="s">
         <v>175</v>
       </c>
-      <c r="D13" s="47"/>
-      <c r="E13" s="47"/>
-      <c r="F13" s="47"/>
-      <c r="G13" s="47"/>
-      <c r="H13" s="47"/>
+      <c r="D13" s="45"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="45"/>
+      <c r="H13" s="45"/>
       <c r="I13" s="11"/>
       <c r="J13" s="3"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="45" t="s">
+      <c r="A14" s="58" t="s">
         <v>169</v>
       </c>
-      <c r="B14" s="45"/>
+      <c r="B14" s="58"/>
       <c r="C14" s="37" t="s">
         <v>170</v>
       </c>
@@ -1749,34 +1724,34 @@
       <c r="J14" s="3"/>
     </row>
     <row r="15" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="59" t="s">
+      <c r="A15" s="44" t="s">
         <v>171</v>
       </c>
-      <c r="B15" s="59"/>
-      <c r="C15" s="47" t="s">
+      <c r="B15" s="44"/>
+      <c r="C15" s="45" t="s">
         <v>174</v>
       </c>
-      <c r="D15" s="47"/>
-      <c r="E15" s="47"/>
-      <c r="F15" s="47"/>
-      <c r="G15" s="47"/>
-      <c r="H15" s="47"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="45"/>
       <c r="I15" s="11"/>
       <c r="J15" s="3"/>
     </row>
     <row r="16" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="59" t="s">
+      <c r="A16" s="44" t="s">
         <v>172</v>
       </c>
-      <c r="B16" s="59"/>
-      <c r="C16" s="60" t="s">
+      <c r="B16" s="44"/>
+      <c r="C16" s="46" t="s">
         <v>173</v>
       </c>
-      <c r="D16" s="60"/>
-      <c r="E16" s="60"/>
-      <c r="F16" s="60"/>
-      <c r="G16" s="60"/>
-      <c r="H16" s="60"/>
+      <c r="D16" s="46"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="46"/>
+      <c r="G16" s="46"/>
+      <c r="H16" s="46"/>
       <c r="I16" s="11"/>
       <c r="J16" s="3"/>
     </row>
@@ -1819,20 +1794,20 @@
       <c r="D20" s="12"/>
     </row>
     <row r="21" spans="1:10" s="3" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="50" t="s">
+      <c r="A21" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="B21" s="50"/>
-      <c r="C21" s="50"/>
-      <c r="D21" s="50"/>
-      <c r="E21" s="53" t="s">
+      <c r="B21" s="42"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="F21" s="53"/>
-      <c r="G21" s="53" t="s">
+      <c r="F21" s="43"/>
+      <c r="G21" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="H21" s="53"/>
+      <c r="H21" s="43"/>
     </row>
     <row r="22" spans="1:10" s="3" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
@@ -1841,88 +1816,88 @@
       <c r="B22" s="21"/>
       <c r="C22" s="21"/>
       <c r="D22" s="22"/>
-      <c r="E22" s="51" t="s">
+      <c r="E22" s="50" t="s">
         <v>187</v>
       </c>
-      <c r="F22" s="51"/>
-      <c r="G22" s="50" t="s">
+      <c r="F22" s="50"/>
+      <c r="G22" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="H22" s="50"/>
+      <c r="H22" s="42"/>
     </row>
     <row r="23" spans="1:10" s="3" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="56" t="s">
+      <c r="A23" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="57"/>
-      <c r="C23" s="57"/>
-      <c r="D23" s="58"/>
-      <c r="E23" s="51" t="s">
+      <c r="B23" s="48"/>
+      <c r="C23" s="48"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="50" t="s">
         <v>188</v>
       </c>
-      <c r="F23" s="51"/>
-      <c r="G23" s="50" t="s">
+      <c r="F23" s="50"/>
+      <c r="G23" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="H23" s="50"/>
+      <c r="H23" s="42"/>
     </row>
     <row r="24" spans="1:10" s="3" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="56" t="s">
+      <c r="A24" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="B24" s="57"/>
-      <c r="C24" s="57"/>
-      <c r="D24" s="58"/>
-      <c r="E24" s="51" t="s">
+      <c r="B24" s="48"/>
+      <c r="C24" s="48"/>
+      <c r="D24" s="49"/>
+      <c r="E24" s="50" t="s">
         <v>189</v>
       </c>
-      <c r="F24" s="51"/>
-      <c r="G24" s="50" t="s">
+      <c r="F24" s="50"/>
+      <c r="G24" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="H24" s="50"/>
+      <c r="H24" s="42"/>
     </row>
     <row r="25" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="56" t="s">
+      <c r="A25" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="B25" s="57"/>
-      <c r="C25" s="57"/>
-      <c r="D25" s="58"/>
-      <c r="E25" s="49"/>
-      <c r="F25" s="49"/>
-      <c r="G25" s="50" t="s">
+      <c r="B25" s="48"/>
+      <c r="C25" s="48"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="53"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="H25" s="50"/>
+      <c r="H25" s="42"/>
     </row>
     <row r="26" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="56" t="s">
+      <c r="A26" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="B26" s="57"/>
-      <c r="C26" s="57"/>
-      <c r="D26" s="58"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="49"/>
-      <c r="G26" s="50" t="s">
+      <c r="B26" s="48"/>
+      <c r="C26" s="48"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="H26" s="50"/>
+      <c r="H26" s="42"/>
     </row>
     <row r="27" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="48" t="s">
+      <c r="A27" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="B27" s="48"/>
-      <c r="C27" s="48"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="49"/>
-      <c r="F27" s="49"/>
-      <c r="G27" s="50">
+      <c r="B27" s="60"/>
+      <c r="C27" s="60"/>
+      <c r="D27" s="60"/>
+      <c r="E27" s="53"/>
+      <c r="F27" s="53"/>
+      <c r="G27" s="42">
         <v>5</v>
       </c>
-      <c r="H27" s="50"/>
+      <c r="H27" s="42"/>
     </row>
     <row r="28" spans="1:10" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
@@ -1964,7 +1939,7 @@
     </row>
     <row r="31" spans="1:10" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="B31" s="13"/>
       <c r="C31" s="17"/>
@@ -1978,7 +1953,7 @@
     </row>
     <row r="32" spans="1:10" s="19" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="B32" s="13"/>
       <c r="C32" s="13"/>
@@ -2052,27 +2027,27 @@
       <c r="I37" s="3"/>
     </row>
     <row r="38" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="53" t="s">
+      <c r="A38" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="B38" s="53" t="s">
+      <c r="B38" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="50" t="s">
+      <c r="C38" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="D38" s="50"/>
-      <c r="E38" s="50"/>
-      <c r="F38" s="50"/>
-      <c r="G38" s="54" t="s">
+      <c r="D38" s="42"/>
+      <c r="E38" s="42"/>
+      <c r="F38" s="42"/>
+      <c r="G38" s="51" t="s">
         <v>26</v>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A39" s="53"/>
-      <c r="B39" s="53"/>
+      <c r="A39" s="43"/>
+      <c r="B39" s="43"/>
       <c r="C39" s="2" t="s">
         <v>22</v>
       </c>
@@ -2085,7 +2060,7 @@
       <c r="F39" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G39" s="55"/>
+      <c r="G39" s="52"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
     </row>
@@ -2790,17 +2765,17 @@
       <c r="I71" s="3"/>
     </row>
     <row r="72" spans="1:9" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A72" s="43" t="s">
+      <c r="A72" s="56" t="s">
         <v>156</v>
       </c>
-      <c r="B72" s="43"/>
+      <c r="B72" s="56"/>
       <c r="C72" s="28" t="s">
         <v>157</v>
       </c>
-      <c r="D72" s="44" t="s">
+      <c r="D72" s="57" t="s">
         <v>158</v>
       </c>
-      <c r="E72" s="44"/>
+      <c r="E72" s="57"/>
       <c r="F72" s="29" t="s">
         <v>159</v>
       </c>
@@ -2809,40 +2784,13 @@
       <c r="B74" s="30" t="s">
         <v>160</v>
       </c>
-      <c r="C74" s="44" t="s">
+      <c r="C74" s="57" t="s">
         <v>161</v>
       </c>
-      <c r="D74" s="44"/>
+      <c r="D74" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:H15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:H16"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A5:H5"/>
     <mergeCell ref="A8:H8"/>
     <mergeCell ref="A72:B72"/>
     <mergeCell ref="D72:E72"/>
@@ -2859,6 +2807,33 @@
     <mergeCell ref="E22:F22"/>
     <mergeCell ref="G22:H22"/>
     <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:H15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:H16"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.78740157480314965" right="0.39370078740157483" top="0.39370078740157483" bottom="0.59055118110236227" header="0.51181102362204722" footer="0.31496062992125984"/>
